--- a/P_S 12V, 5V, 3.3V/V_1_0/Pcb FIle/BOM.xlsx
+++ b/P_S 12V, 5V, 3.3V/V_1_0/Pcb FIle/BOM.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PER_S\Power Supply\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pcb-portfolio\P_S 12V, 5V, 3.3V\V_1_0\Pcb FIle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B1823D4-9E01-443D-91B9-7E6EA4A635CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF8E3AA-67B6-4425-B8D1-CCF69458628C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F90D8321-0BE9-421B-ACCE-F27D770590DE}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>SR</t>
   </si>
@@ -65,26 +63,53 @@
     <t>ADD. INFROMATION</t>
   </si>
   <si>
-    <t>XY308-2.54-XINYA-2 Pin Screw Terminal Block</t>
+    <t>HLK-10M12</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>https://robu.in/product/ac-dc-12v-10w-step-down-mini-power-supply-module-converter-intelligent-household-switch-power-module-hlk-10m12/?gad_source=1&amp;gad_campaignid=17427802559&amp;gbraid=0AAAAADvLFWdmf28lzzaPLwXrivEZe7tF9&amp;gclid=Cj0KCQiAy6vMBhDCARIsAK8rOgk74Ukklw2VLAaILk1dfR1Z-_szGcqKGXWifvU5_EVySraAkFoeD6kaAsXnEALw_wcB</t>
+  </si>
+  <si>
+    <t>https://robu.in/product/36913150000-littelfuse-36913150000-fuse-pcb-leaded-3-15-a-300-v-te5-369-series-time-delay-radial-leaded/</t>
+  </si>
+  <si>
+    <t>RADIAL FUSE</t>
+  </si>
+  <si>
+    <t>DIP</t>
+  </si>
+  <si>
+    <t>MOV-9D561K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCREW TERMINAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIP </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="19.600000000000001"/>
-      <color rgb="FF333E48"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -122,13 +147,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176FF809-5BD8-4A6F-9A09-E5307AA4C635}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.77734375" customWidth="1"/>
@@ -477,7 +499,7 @@
     <col min="9" max="9" width="26.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,70 +528,114 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="98.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I2" s="1"/>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="E6" s="1">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -580,7 +646,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -591,7 +657,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -602,7 +668,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -613,7 +679,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -624,7 +690,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -635,7 +701,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -646,7 +712,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -657,7 +723,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -668,7 +734,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -767,17 +833,6 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
